--- a/docs/Mapping_casi_uso/morte/Morte_011.xlsx
+++ b/docs/Mapping_casi_uso/morte/Morte_011.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1162" uniqueCount="222">
   <si>
     <t>Sezione</t>
   </si>
@@ -213,6 +213,12 @@
   </si>
   <si>
     <t>testoDataPresuntaMorte</t>
+  </si>
+  <si>
+    <t>Data rinvenimento cadavere</t>
+  </si>
+  <si>
+    <t>dataRinvenimentoCadavere</t>
   </si>
   <si>
     <t>Luogo</t>
@@ -730,7 +736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H166"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.1015625" customWidth="true" bestFit="true"/>
@@ -1417,7 +1423,7 @@
         <v>69</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>55</v>
@@ -1463,7 +1469,7 @@
         <v>73</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>55</v>
@@ -1595,19 +1601,19 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="C38" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>10</v>
@@ -1618,16 +1624,16 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>90</v>
@@ -1641,7 +1647,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>91</v>
@@ -1650,7 +1656,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>92</v>
@@ -1664,19 +1670,19 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>10</v>
@@ -1687,19 +1693,19 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>10</v>
@@ -1710,16 +1716,16 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>96</v>
@@ -1733,16 +1739,16 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>98</v>
@@ -1756,19 +1762,19 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>10</v>
@@ -1779,10 +1785,10 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>9</v>
@@ -1791,7 +1797,7 @@
         <v>103</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>10</v>
@@ -1802,19 +1808,19 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>10</v>
@@ -1825,7 +1831,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>106</v>
@@ -1834,7 +1840,7 @@
         <v>28</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>107</v>
@@ -1848,7 +1854,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>108</v>
@@ -1857,7 +1863,7 @@
         <v>28</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>109</v>
@@ -1871,7 +1877,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>110</v>
@@ -1880,7 +1886,7 @@
         <v>28</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>111</v>
@@ -1894,19 +1900,19 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C51" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>10</v>
@@ -1917,16 +1923,16 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>117</v>
@@ -1940,16 +1946,16 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>119</v>
@@ -1963,7 +1969,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>120</v>
@@ -1972,7 +1978,7 @@
         <v>28</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>121</v>
@@ -1986,16 +1992,16 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>123</v>
@@ -2009,16 +2015,16 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>125</v>
@@ -2032,7 +2038,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>126</v>
@@ -2041,7 +2047,7 @@
         <v>28</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>127</v>
@@ -2055,16 +2061,16 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>129</v>
@@ -2078,7 +2084,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>130</v>
@@ -2087,7 +2093,7 @@
         <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>131</v>
@@ -2101,7 +2107,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>132</v>
@@ -2110,7 +2116,7 @@
         <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>133</v>
@@ -2124,16 +2130,16 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>134</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>135</v>
@@ -2147,7 +2153,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>136</v>
@@ -2156,7 +2162,7 @@
         <v>28</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>137</v>
@@ -2170,7 +2176,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>138</v>
@@ -2179,7 +2185,7 @@
         <v>28</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>139</v>
@@ -2193,7 +2199,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>140</v>
@@ -2202,7 +2208,7 @@
         <v>28</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>141</v>
@@ -2216,19 +2222,19 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>10</v>
@@ -2239,16 +2245,16 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>144</v>
@@ -2262,7 +2268,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>145</v>
@@ -2271,7 +2277,7 @@
         <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>146</v>
@@ -2285,16 +2291,16 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>147</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>148</v>
@@ -2308,7 +2314,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>149</v>
@@ -2317,7 +2323,7 @@
         <v>28</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>150</v>
@@ -2331,7 +2337,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>151</v>
@@ -2340,7 +2346,7 @@
         <v>28</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>152</v>
@@ -2354,7 +2360,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>153</v>
@@ -2363,7 +2369,7 @@
         <v>28</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>154</v>
@@ -2377,7 +2383,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>155</v>
@@ -2386,7 +2392,7 @@
         <v>28</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>156</v>
@@ -2400,7 +2406,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>157</v>
@@ -2409,7 +2415,7 @@
         <v>28</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>158</v>
@@ -2423,7 +2429,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>159</v>
@@ -2432,7 +2438,7 @@
         <v>28</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>160</v>
@@ -2446,7 +2452,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>161</v>
@@ -2455,7 +2461,7 @@
         <v>28</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>162</v>
@@ -2469,7 +2475,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>163</v>
@@ -2478,7 +2484,7 @@
         <v>28</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>164</v>
@@ -2492,7 +2498,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>165</v>
@@ -2501,7 +2507,7 @@
         <v>28</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>166</v>
@@ -2515,7 +2521,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>167</v>
@@ -2524,7 +2530,7 @@
         <v>28</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>168</v>
@@ -2538,7 +2544,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>169</v>
@@ -2547,7 +2553,7 @@
         <v>28</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>170</v>
@@ -2561,19 +2567,19 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="C80" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D80" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E80" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>10</v>
@@ -2584,19 +2590,19 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>10</v>
@@ -2607,19 +2613,19 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>10</v>
@@ -2630,16 +2636,16 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>90</v>
@@ -2653,7 +2659,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>91</v>
@@ -2662,7 +2668,7 @@
         <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>92</v>
@@ -2676,19 +2682,19 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>10</v>
@@ -2699,7 +2705,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>106</v>
@@ -2708,7 +2714,7 @@
         <v>28</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>107</v>
@@ -2722,7 +2728,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>108</v>
@@ -2731,7 +2737,7 @@
         <v>28</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>109</v>
@@ -2745,7 +2751,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>110</v>
@@ -2754,7 +2760,7 @@
         <v>28</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>111</v>
@@ -2768,19 +2774,19 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>10</v>
@@ -2794,7 +2800,7 @@
         <v>173</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>28</v>
@@ -2803,27 +2809,27 @@
         <v>174</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>175</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>117</v>
@@ -2832,35 +2838,35 @@
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>122</v>
@@ -2869,7 +2875,7 @@
         <v>28</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>123</v>
@@ -2878,12 +2884,12 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>124</v>
@@ -2892,7 +2898,7 @@
         <v>28</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>125</v>
@@ -2901,12 +2907,12 @@
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>126</v>
@@ -2915,7 +2921,7 @@
         <v>28</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>127</v>
@@ -2924,12 +2930,12 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>128</v>
@@ -2938,7 +2944,7 @@
         <v>28</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>129</v>
@@ -2947,21 +2953,21 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>131</v>
@@ -2970,21 +2976,21 @@
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>133</v>
@@ -2993,21 +2999,21 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>135</v>
@@ -3016,21 +3022,21 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>137</v>
@@ -3039,21 +3045,21 @@
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>139</v>
@@ -3062,21 +3068,21 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>141</v>
@@ -3085,44 +3091,44 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>81</v>
+        <v>183</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>144</v>
@@ -3131,21 +3137,21 @@
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>182</v>
+        <v>145</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>146</v>
@@ -3154,67 +3160,67 @@
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>184</v>
+        <v>148</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>147</v>
+        <v>185</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>185</v>
+        <v>149</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>150</v>
@@ -3223,21 +3229,21 @@
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>152</v>
@@ -3246,21 +3252,21 @@
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>154</v>
@@ -3269,21 +3275,21 @@
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>156</v>
@@ -3292,21 +3298,21 @@
         <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>158</v>
@@ -3315,21 +3321,21 @@
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>160</v>
@@ -3338,21 +3344,21 @@
         <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>162</v>
@@ -3361,35 +3367,35 @@
         <v>10</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>194</v>
@@ -3398,7 +3404,7 @@
         <v>28</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>195</v>
@@ -3407,12 +3413,12 @@
         <v>10</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>196</v>
@@ -3421,7 +3427,7 @@
         <v>28</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>197</v>
@@ -3430,44 +3436,44 @@
         <v>10</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B118" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B118" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="C118" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>115</v>
+        <v>199</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>117</v>
@@ -3476,35 +3482,35 @@
         <v>10</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>122</v>
@@ -3513,7 +3519,7 @@
         <v>28</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>123</v>
@@ -3522,12 +3528,12 @@
         <v>10</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>124</v>
@@ -3536,7 +3542,7 @@
         <v>28</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>125</v>
@@ -3545,12 +3551,12 @@
         <v>10</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>126</v>
@@ -3559,7 +3565,7 @@
         <v>28</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>127</v>
@@ -3568,12 +3574,12 @@
         <v>10</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>128</v>
@@ -3582,7 +3588,7 @@
         <v>28</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>129</v>
@@ -3591,21 +3597,21 @@
         <v>10</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>131</v>
@@ -3614,21 +3620,21 @@
         <v>10</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>133</v>
@@ -3637,21 +3643,21 @@
         <v>10</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>135</v>
@@ -3660,21 +3666,21 @@
         <v>10</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>137</v>
@@ -3683,21 +3689,21 @@
         <v>10</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>139</v>
@@ -3706,21 +3712,21 @@
         <v>10</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>141</v>
@@ -3729,44 +3735,44 @@
         <v>10</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>81</v>
+        <v>183</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>144</v>
@@ -3775,21 +3781,21 @@
         <v>10</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>182</v>
+        <v>145</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>146</v>
@@ -3798,67 +3804,67 @@
         <v>10</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>184</v>
+        <v>148</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>147</v>
+        <v>185</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>185</v>
+        <v>149</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>150</v>
@@ -3867,21 +3873,21 @@
         <v>10</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>152</v>
@@ -3890,21 +3896,21 @@
         <v>10</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>154</v>
@@ -3913,21 +3919,21 @@
         <v>10</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>156</v>
@@ -3936,21 +3942,21 @@
         <v>10</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>158</v>
@@ -3959,21 +3965,21 @@
         <v>10</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>160</v>
@@ -3982,21 +3988,21 @@
         <v>10</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>162</v>
@@ -4005,35 +4011,35 @@
         <v>10</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>194</v>
@@ -4042,7 +4048,7 @@
         <v>28</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>195</v>
@@ -4051,12 +4057,12 @@
         <v>10</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>196</v>
@@ -4065,7 +4071,7 @@
         <v>28</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>197</v>
@@ -4074,7 +4080,7 @@
         <v>10</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="146">
@@ -4082,39 +4088,39 @@
         <v>200</v>
       </c>
       <c r="B146" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G146" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F146" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G146" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>203</v>
+        <v>104</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>10</v>
@@ -4125,19 +4131,19 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B148" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>10</v>
@@ -4148,7 +4154,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>207</v>
@@ -4157,7 +4163,7 @@
         <v>9</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>208</v>
@@ -4171,338 +4177,338 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B150" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B150" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="C150" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D150" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E150" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="E150" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="F150" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>211</v>
+        <v>19</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D163" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="E163" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G163" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D163" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E163" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F163" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G163" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B164" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D164" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D164" s="2" t="s">
-        <v>214</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>217</v>
@@ -4516,7 +4522,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>218</v>
@@ -4525,7 +4531,7 @@
         <v>28</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>219</v>
@@ -4534,6 +4540,29 @@
         <v>10</v>
       </c>
       <c r="G165" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G166" s="2" t="s">
         <v>19</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/morte/Morte_011.xlsx
+++ b/docs/Mapping_casi_uso/morte/Morte_011.xlsx
@@ -1078,7 +1078,7 @@
         <v>39</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>29</v>
